--- a/data/example/checkin/weight_loss/eps_chat_history.xlsx
+++ b/data/example/checkin/weight_loss/eps_chat_history.xlsx
@@ -474,14 +474,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>今天完成了25分钟快走和拉伸。</t>
+          <t>今天完成了22分钟快走和拉伸，晚餐控制得还可以。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-11 19:07</t>
+          <t>2026-03-11 12:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>@Ivy #exercise_feedback 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Ivy #exercise_feedback 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11 19:10</t>
+          <t>2026-03-11 15:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>@Ivy #exercise_feedback 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Ivy #exercise_feedback 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
@@ -562,14 +562,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>今天完成了30分钟快走和拉伸。</t>
+          <t>上午散步26分钟，晚上又补了力量训练，感觉状态不错。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12 19:25</t>
+          <t>2026-03-12 13:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -584,14 +584,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>@Julia #exercise_feedback 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Julia #exercise_feedback 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12 19:28</t>
+          <t>2026-03-12 16:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>@Julia #exercise_feedback 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Julia #exercise_feedback 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>@Julia #exercise_feedback 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Julia #exercise_feedback 做得很好。根据你这周的记录，今天已经完成约36分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我会按建议把饭后步行也加上。</t>
         </is>
       </c>
     </row>
@@ -672,14 +672,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>今天完成了35分钟快走和拉伸。</t>
+          <t>今天步数大概有6150步，还做了拉伸和深蹲。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-13 19:46</t>
+          <t>2026-03-13 11:46</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -694,14 +694,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>@Kara #exercise_feedback 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Kara #exercise_feedback 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-13 19:49</t>
+          <t>2026-03-13 14:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -716,14 +716,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>@Kara #exercise_feedback 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Kara #exercise_feedback 做得很好。根据你这周的记录，今天已经完成约35分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13 19:52</t>
+          <t>2026-03-13 17:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>@Kara #exercise_feedback 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Kara #exercise_feedback 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>明白了，我会继续保持今天的节奏。</t>
         </is>
       </c>
     </row>
@@ -782,14 +782,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>今天完成了40分钟快走和拉伸。</t>
+          <t>今天按照计划完成了有氧训练，运动后没有加餐。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-14 19:07</t>
+          <t>2026-03-14 12:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>@Luna #exercise_feedback 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Luna #exercise_feedback 做得很好。根据你这周的记录，今天已经完成约34分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-14 19:10</t>
+          <t>2026-03-14 15:10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -826,14 +826,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>@Luna #exercise_feedback 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Luna #exercise_feedback 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-14 19:13</t>
+          <t>2026-03-14 18:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -848,14 +848,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>@Luna #exercise_feedback 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Luna #exercise_feedback 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-14 19:16</t>
+          <t>2026-03-14 21:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>@Luna #exercise_feedback 已记录，今天第4次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Luna #exercise_feedback 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
@@ -914,14 +914,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>今天完成了45分钟快走和拉伸。</t>
+          <t>今天完成了38分钟快走和拉伸，晚餐控制得还可以。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-15 19:31</t>
+          <t>2026-03-15 13:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -936,14 +936,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>@Mia #exercise_feedback 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Mia #exercise_feedback 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-15 19:34</t>
+          <t>2026-03-15 16:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>@Mia #exercise_feedback 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Mia #exercise_feedback 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
@@ -980,14 +980,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>@Mia #exercise_feedback 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Mia #exercise_feedback 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-15 19:40</t>
+          <t>2026-03-15 21:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>@Mia #exercise_feedback 已记录，今天第4次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Mia #exercise_feedback 做得很好。根据你这周的记录，今天已经完成约53分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我会按建议把饭后步行也加上。</t>
         </is>
       </c>
     </row>
@@ -1046,14 +1046,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>今天完成了50分钟快走和拉伸。</t>
+          <t>上午散步42分钟，晚上又补了力量训练，感觉状态不错。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16 19:55</t>
+          <t>2026-03-16 11:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>@Nora #exercise_feedback 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Nora #exercise_feedback 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16 19:58</t>
+          <t>2026-03-16 14:58</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1090,14 +1090,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>@Nora #exercise_feedback 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Nora #exercise_feedback 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16 19:01</t>
+          <t>2026-03-16 17:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1112,14 +1112,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>@Nora #exercise_feedback 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Nora #exercise_feedback 做得很好。根据你这周的记录，今天已经完成约52分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16 19:04</t>
+          <t>2026-03-16 20:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1134,14 +1134,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>@Nora #exercise_feedback 已记录，今天第4次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Nora #exercise_feedback 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16 19:07</t>
+          <t>2026-03-16 21:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>@Nora #exercise_feedback 已记录，今天第5次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Nora #exercise_feedback 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>明白了，我会继续保持今天的节奏。</t>
         </is>
       </c>
     </row>
@@ -1200,14 +1200,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>今天完成了55分钟快走和拉伸。</t>
+          <t>今天步数大概有8750步，还做了拉伸和深蹲。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-17 19:22</t>
+          <t>2026-03-17 12:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1222,14 +1222,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>@Olive #exercise_feedback 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Olive #exercise_feedback 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-17 19:25</t>
+          <t>2026-03-17 15:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1244,14 +1244,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>@Olive #exercise_feedback 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Olive #exercise_feedback 做得很好。根据你这周的记录，今天已经完成约51分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-17 19:28</t>
+          <t>2026-03-17 18:28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>@Olive #exercise_feedback 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Olive #exercise_feedback 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
@@ -1310,14 +1310,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>今天完成了60分钟快走和拉伸。</t>
+          <t>今天按照计划完成了有氧训练，运动后没有加餐。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-18 19:43</t>
+          <t>2026-03-18 13:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1332,14 +1332,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>@Piper #exercise_feedback 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Piper #exercise_feedback 做得很好。根据你这周的记录，今天已经完成约50分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-18 19:46</t>
+          <t>2026-03-18 16:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>@Piper #exercise_feedback 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Piper #exercise_feedback 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>@Piper #exercise_feedback 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Piper #exercise_feedback 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-18 19:52</t>
+          <t>2026-03-18 21:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1398,14 +1398,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>@Piper #exercise_feedback 已记录，今天第4次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Piper #exercise_feedback 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-18 19:55</t>
+          <t>2026-03-18 21:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>@Piper #exercise_feedback 已记录，今天第5次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Piper #exercise_feedback 做得很好。根据你这周的记录，今天已经完成约70分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我会按建议把饭后步行也加上。</t>
         </is>
       </c>
     </row>
